--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/07 12:28:03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>58823</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>58823.53</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58823.53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>58823</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>58823.53</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>58823.53</t>
+          <t>590000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>58823</t>
+          <t>69411.76</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>58823</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.53</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10588.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>590000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>69411.76</t>
+          <t>590000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>58823</t>
+          <t>69411.76</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>69411</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>10588.76</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,237 +117,279 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>590000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>69411.76</t>
+          <t>760000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>69411</t>
+          <t>89893.69</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>69411</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.76</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20482.69</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -313,83 +313,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>760000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89893.69</t>
+          <t>760000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>69411</t>
+          <t>89893.69</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>89892</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>20482.69</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1.69</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,17 +95,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,166 +159,181 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -340,83 +355,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>760000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89893.69</t>
+          <t>975000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>89892</t>
+          <t>115797.31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>89892</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1.69</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>25905.31</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -343,7 +343,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -355,12 +355,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -382,83 +382,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>975000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>115797.31</t>
+          <t>975000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89892</t>
+          <t>115797.31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>115795</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>25905.31</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2.31</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,17 +137,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,166 +201,181 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -370,7 +385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -382,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -409,83 +424,110 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>975000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>115797.31</t>
+          <t>1065000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>115795</t>
+          <t>126511.59</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>115795</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2.31</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>10716.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -412,7 +412,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -424,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -451,83 +451,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1065000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>126511.59</t>
+          <t>1065000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>115795</t>
+          <t>126511.59</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>126509</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>10716.59</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,17 +179,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -439,7 +454,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -451,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -478,83 +493,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1065000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>126511.59</t>
+          <t>1165000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>126509</t>
+          <t>138559.79</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>126509</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2.59</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12050.79</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -493,12 +493,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -520,83 +520,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1165000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>138559.79</t>
+          <t>1165000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>126509</t>
+          <t>138559.79</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>139357</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>12050.79</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>-797.21</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,12 +493,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -520,12 +520,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -547,83 +547,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1165000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>138559.79</t>
+          <t>1165000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>139357</t>
+          <t>138559.79</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>151405</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>-797.21</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>-12845.21</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,17 +221,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -520,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -535,7 +550,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -547,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -574,83 +589,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1165000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>138559.79</t>
+          <t>1415000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>151405</t>
+          <t>168680.27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>151405</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>-12845.21</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>17275.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -589,12 +589,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -616,83 +616,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1415000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>168680.27</t>
+          <t>1415000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>151405</t>
+          <t>168680.27</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>181525</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>17275.27</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>-12844.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,17 +95,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,17 +263,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -589,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -604,7 +619,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -616,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -643,83 +658,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1415000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>168680.27</t>
+          <t>1505000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>181525</t>
+          <t>179523.64</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>181525</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>-12844.73</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>-2001.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -496,12 +496,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -658,12 +658,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -685,83 +685,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1505000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>179523.64</t>
+          <t>1505000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>181525</t>
+          <t>179523.64</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>192368</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>-2001.36</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>-12844.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,17 +137,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,17 +305,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,22 +342,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -658,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -673,7 +688,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -685,12 +700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -712,83 +727,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1505000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>179523.64</t>
+          <t>1585000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>192368</t>
+          <t>189162.19</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>192368</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>-12844.36</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-3205.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -538,12 +538,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -565,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -592,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -619,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -673,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,12 +700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -727,12 +727,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -754,83 +754,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1585000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>189162.19</t>
+          <t>1585000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>192368</t>
+          <t>189162.19</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>202006</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>-3205.81</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>-12843.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,12 +137,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,17 +179,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,17 +347,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,22 +384,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,166 +411,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -592,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -619,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -673,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -727,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -742,7 +757,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -754,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -781,83 +796,110 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1585000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>189162.19</t>
+          <t>1685000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>202006</t>
+          <t>201066.96</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>202006</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>-12843.81</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>-939.04</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -796,12 +796,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -823,83 +823,110 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1685000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>201066.96</t>
+          <t>1685000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>202006</t>
+          <t>201066.96</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>213910</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>-939.04</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>-12843.04</t>
         </is>
       </c>
     </row>
